--- a/artfynd/A 39071-2023 artfynd.xlsx
+++ b/artfynd/A 39071-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39071-2023 artfynd.xlsx
+++ b/artfynd/A 39071-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55773987</v>
+        <v>105343603</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1,3 km SSV om Stensjö, Ång</t>
+          <t>Gideåberg värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570938.6930111593</v>
+        <v>570896</v>
       </c>
       <c r="R2" t="n">
-        <v>7014438.728082873</v>
+        <v>7014503</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,80 +756,52 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105343609</v>
+        <v>105343610</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -854,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570942.4499094065</v>
+        <v>570972</v>
       </c>
       <c r="R3" t="n">
-        <v>7014432.051574246</v>
+        <v>7014434</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,19 +844,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105343587</v>
+        <v>105343616</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -970,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570839.5961497438</v>
+        <v>570916</v>
       </c>
       <c r="R4" t="n">
-        <v>7014574.43266216</v>
+        <v>7014327</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1003,19 +945,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105343603</v>
+        <v>105343622</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,12 +998,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570896.6644051624</v>
+        <v>570862</v>
       </c>
       <c r="R5" t="n">
-        <v>7014503.14141164</v>
+        <v>7014106</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,19 +1046,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105343622</v>
+        <v>105343588</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1202,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570861.63592734</v>
+        <v>570826</v>
       </c>
       <c r="R6" t="n">
-        <v>7014105.812278185</v>
+        <v>7014595</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,19 +1147,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105343600</v>
+        <v>55773987</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>1,3 km SSV om Stensjö, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570838.7325686886</v>
+        <v>570939</v>
       </c>
       <c r="R7" t="n">
-        <v>7014490.601611203</v>
+        <v>7014439</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,27 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hane</t>
+          <t>2015-09-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,73 +1261,91 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering Y-län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105343621</v>
+        <v>55773988</v>
       </c>
       <c r="B8" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>1,3 km SSV om Stensjö, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570860.6248195034</v>
+        <v>571118</v>
       </c>
       <c r="R8" t="n">
-        <v>7014110.747316378</v>
+        <v>7014529</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,22 +1369,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,57 +1385,75 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering Y-län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105343619</v>
+        <v>105343587</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1555,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570835.26499167</v>
+        <v>570840</v>
       </c>
       <c r="R9" t="n">
-        <v>7014299.46179323</v>
+        <v>7014575</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1588,19 +1496,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,15 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105343610</v>
+        <v>105343598</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1671,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570972.6380440737</v>
+        <v>570989</v>
       </c>
       <c r="R10" t="n">
-        <v>7014434.06844709</v>
+        <v>7014622</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1704,19 +1597,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,37 +1630,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105343604</v>
+        <v>105343617</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1787,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570898.4684194695</v>
+        <v>570910</v>
       </c>
       <c r="R11" t="n">
-        <v>7014503.181120184</v>
+        <v>7014325</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1820,19 +1698,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,37 +1731,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105343608</v>
+        <v>105343618</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1903,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570945.3887587951</v>
+        <v>570885</v>
       </c>
       <c r="R12" t="n">
-        <v>7014442.029865348</v>
+        <v>7014317</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1936,19 +1799,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,53 +1832,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105343586</v>
+        <v>118094795</v>
       </c>
       <c r="B13" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gideåberg värdetrakt, Ång</t>
+          <t>Tvärsförmyran, Tvärsförmyran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570842.7332925921</v>
+        <v>570789</v>
       </c>
       <c r="R13" t="n">
-        <v>7014575.402854617</v>
+        <v>7014580</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,22 +1897,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,31 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105343601</v>
+        <v>105343620</v>
       </c>
       <c r="B14" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,16 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2130,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570890.6427561711</v>
+        <v>570838</v>
       </c>
       <c r="R14" t="n">
-        <v>7014510.218578008</v>
+        <v>7014296</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2163,19 +1997,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,19 +2030,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105343620</v>
+        <v>105343621</v>
       </c>
       <c r="B15" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2231,12 +2050,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570838.5113625888</v>
+        <v>570860</v>
       </c>
       <c r="R15" t="n">
-        <v>7014295.47746612</v>
+        <v>7014111</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2279,19 +2098,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,37 +2131,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105343607</v>
+        <v>105343599</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2362,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570951.3953747563</v>
+        <v>570990</v>
       </c>
       <c r="R16" t="n">
-        <v>7014456.131230467</v>
+        <v>7014568</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2395,19 +2199,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,37 +2232,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105343605</v>
+        <v>105343611</v>
       </c>
       <c r="B17" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2478,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570973.8510583563</v>
+        <v>571045</v>
       </c>
       <c r="R17" t="n">
-        <v>7014481.409625256</v>
+        <v>7014338</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2511,19 +2300,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,15 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105343599</v>
+        <v>105343623</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2594,10 +2368,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570990.0052559908</v>
+        <v>570822</v>
       </c>
       <c r="R18" t="n">
-        <v>7014567.380495589</v>
+        <v>7014137</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2627,19 +2401,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2670,37 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105343602</v>
+        <v>105343586</v>
       </c>
       <c r="B19" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2710,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570891.5645868703</v>
+        <v>570843</v>
       </c>
       <c r="R19" t="n">
-        <v>7014509.337654841</v>
+        <v>7014576</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2743,19 +2502,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,37 +2535,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105343611</v>
+        <v>105343604</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2826,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571044.6908244959</v>
+        <v>570899</v>
       </c>
       <c r="R20" t="n">
-        <v>7014338.322039077</v>
+        <v>7014503</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2859,19 +2603,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,37 +2636,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105343618</v>
+        <v>105343605</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2942,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570884.9628096002</v>
+        <v>570974</v>
       </c>
       <c r="R21" t="n">
-        <v>7014317.228494057</v>
+        <v>7014481</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2975,19 +2704,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,12 +2740,7 @@
         <v>105343606</v>
       </c>
       <c r="B22" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,10 +2772,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570974.1884835568</v>
+        <v>570974</v>
       </c>
       <c r="R22" t="n">
-        <v>7014466.096266411</v>
+        <v>7014466</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3091,19 +2805,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3134,37 +2838,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105343623</v>
+        <v>105343607</v>
       </c>
       <c r="B23" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3174,10 +2873,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570822.1318316171</v>
+        <v>570951</v>
       </c>
       <c r="R23" t="n">
-        <v>7014137.391058456</v>
+        <v>7014456</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3207,19 +2906,9 @@
           <t>2022-11-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-11-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,6 +2932,904 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>105343608</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570945</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7014442</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>105343609</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570943</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7014432</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>105343619</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570835</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7014300</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126709241</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sörbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>570970</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7014318</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126709237</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sörbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>571082</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7014508</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126709235</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sörbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>571082</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7014508</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>105343600</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>570839</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7014490</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hane</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126709232</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sörbyn, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>571082</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7014508</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>105343601</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gideåberg värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>570890</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7014510</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 39071-2023 artfynd.xlsx
+++ b/artfynd/A 39071-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343610</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343616</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773987</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55773988</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343587</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,6 +1672,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343598</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,6 +1778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343617</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343618</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118094795</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343620</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343621</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,6 +2304,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343599</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2330,6 +2410,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343611</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343623</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2532,6 +2622,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343586</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343604</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2734,6 +2834,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343605</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343606</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2936,6 +3046,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343607</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3037,6 +3152,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343608</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3138,6 +3258,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343609</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3239,6 +3364,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343619</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3336,6 +3466,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126709241</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3433,6 +3568,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126709237</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126709235</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3636,6 +3781,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343600</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3733,6 +3883,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126709232</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3834,8 +3989,46 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>